--- a/assets/constructions/examples/ctd_mib_t.xlsx
+++ b/assets/constructions/examples/ctd_mib_t.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,11 +599,31 @@
           <t>dbc2</t>
         </is>
       </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TDCW-50-22-6T</t>
+          <t>TDCW-63-22-8T</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -619,7 +639,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
         <v>22</v>
@@ -629,10 +649,10 @@
         <v>50</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -646,7 +666,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="R2" t="n">
         <v>3.2</v>
@@ -699,69 +719,79 @@
         </is>
       </c>
       <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>170.96</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AL2" t="n">
+        <v>12789.19</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12290911600</t>
+          <t>TDCW-80-27-10T</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M94</t>
+          <t>TDCW</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>85</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="G3" t="n">
-        <v>22</v>
-      </c>
-      <c r="H3" t="n">
-        <v>55</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>2.73</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>2.73</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>4.26</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="R3" t="n">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>TNAX1604ZZ..</t>
+          <t>TD16</t>
         </is>
       </c>
       <c r="T3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -775,12 +805,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx022</t>
+          <t>ISO_6462:FDAxx027</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>WIDIA_TNAX1604H</t>
+          <t>DER_TD16H</t>
         </is>
       </c>
       <c r="AA3" t="n">
@@ -793,25 +823,35 @@
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>WID_TNAX1604_H</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>WID_TNAX16_X2</t>
-        </is>
-      </c>
+          <t>TD16_H</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2019 /Novo</t>
+          <t>2019 / DEREK</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>203.03</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AL3" t="n">
+        <v>15188.29</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TDCW-80-27-10T</t>
+          <t>TDCW-50-22-6T</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -827,20 +867,20 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>50</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -854,7 +894,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="R4" t="n">
         <v>3.2</v>
@@ -879,7 +919,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx027</t>
+          <t>ISO_6462:FDAxx022</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -907,65 +947,83 @@
         </is>
       </c>
       <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>147.48</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>11032.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TDCW-63-22-8T</t>
+          <t>12290911600</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TDCW</t>
+          <t>M94</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>85</v>
+      </c>
       <c r="F5" t="n">
         <v>63</v>
       </c>
       <c r="G5" t="n">
         <v>22</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>55</v>
+      </c>
       <c r="I5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>2.73</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2.73</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>4.26</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="R5" t="n">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>TD16</t>
+          <t>TNAX1604ZZ..</t>
         </is>
       </c>
       <c r="T5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -984,7 +1042,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>DER_TD16H</t>
+          <t>WIDIA_TNAX1604H</t>
         </is>
       </c>
       <c r="AA5" t="n">
@@ -997,16 +1055,26 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>TD16_H</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+          <t>WID_TNAX1604_H</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>WID_TNAX16_X2</t>
+        </is>
+      </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
+          <t>2019 /Novo</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
